--- a/Data/processed/total_n_males.xlsx
+++ b/Data/processed/total_n_males.xlsx
@@ -413,7 +413,7 @@
         <v>2002</v>
       </c>
       <c r="B9" t="n">
-        <v>227</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -421,7 +421,7 @@
         <v>2003</v>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -461,7 +461,7 @@
         <v>2008</v>
       </c>
       <c r="B15" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
